--- a/TestData/testdata.xlsx
+++ b/TestData/testdata.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="12">
   <si>
     <t>Username</t>
   </si>

--- a/TestData/testdata.xlsx
+++ b/TestData/testdata.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="12">
   <si>
     <t>Username</t>
   </si>

--- a/TestData/testdata.xlsx
+++ b/TestData/testdata.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="12">
   <si>
     <t>Username</t>
   </si>
